--- a/questionnaire_templates/005_lighting_control_preferences--questionnaire_templates.xlsx
+++ b/questionnaire_templates/005_lighting_control_preferences--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input_1</t>
+          <t>lighting_control_needs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,19 +531,19 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>facility_name_1</t>
+          <t>facility_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>automation_level_1</t>
+          <t>automation_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,24 +577,24 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>automation_level_2</t>
+          <t>lighting_control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Automation Level</t>
+          <t>Lighting Control</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lighting_control_1</t>
+          <t>control_system</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lighting Control</t>
+          <t>Control System</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,159 +630,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>control_system_1</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Control System</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>control_system_2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Control System</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>control_system_3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Control System</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>control_system_4</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Control System</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>notes_1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>notes_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>notes_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,12 +661,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,219 +689,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>facility_name_1_choices</t>
+          <t>facility_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jotform</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jotform</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>facility_name_1_choices</t>
+          <t>facility_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>installers</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Installers</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>facility_name_1_choices</t>
+          <t>facility_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>designers</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Designers</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facility_name_1_choices</t>
+          <t>automation_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>facility_teams</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Facility teams</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>automation_level_1_choices</t>
+          <t>automation_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>automation_level_1_choices</t>
+          <t>automation_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>automation_level_1_choices</t>
+          <t>lighting_control_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>motion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Motion</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>automation_level_2_choices</t>
+          <t>lighting_control_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>dimming</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Dimming</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>automation_level_2_choices</t>
+          <t>lighting_control_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>brightness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>automation_level_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>lighting_control_1_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>motion</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Motion</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>lighting_control_1_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>dimming</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dimming</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>lighting_control_1_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>brightness</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>Brightness</t>
         </is>
